--- a/demo/data/остатки-WB-2026-06-29.xlsx
+++ b/demo/data/остатки-WB-2026-06-29.xlsx
@@ -511,7 +511,7 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>159</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -531,7 +531,7 @@
         <v>1</v>
       </c>
       <c r="F3">
-        <v>140</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -551,7 +551,7 @@
         <v>1</v>
       </c>
       <c r="F4">
-        <v>130</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -571,7 +571,7 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>161</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -591,7 +591,7 @@
         <v>1</v>
       </c>
       <c r="F6">
-        <v>140</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -611,7 +611,7 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>91</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -631,7 +631,7 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>107</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -651,7 +651,7 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>103</v>
+        <v>161</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -671,7 +671,7 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>102</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -691,7 +691,7 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>99</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -711,7 +711,7 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>93</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -731,7 +731,7 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>116</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14" spans="1:6">
